--- a/Result/profitability/1314.xlsx
+++ b/Result/profitability/1314.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07000000000000005</v>
+        <v>-0.1087500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-6.5525</v>
+        <v>-5.84</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1037500000000001</v>
+        <v>-0.1737500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.61</v>
+        <v>-3.922499999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1400000000000001</v>
+        <v>-0.1875000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.4375</v>
+        <v>-3.723749999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.32125</v>
+        <v>-0.3250000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-14.6825</v>
+        <v>-12.69</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2900000000000001</v>
+        <v>-0.3175000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-13.5525</v>
+        <v>-11.37125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1875000000000001</v>
+        <v>-0.2412500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.70125</v>
+        <v>-7.328749999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1237500000000001</v>
+        <v>-0.1725000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.238750000000001</v>
+        <v>-4.699999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>0.27</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.08125000000000006</v>
+        <v>-0.08125000000000007</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.4175</v>
+        <v>-4.417499999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,10 +1645,10 @@
         <v>0.41</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07250000000000006</v>
+        <v>-0.07250000000000009</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.673750000000001</v>
+        <v>-3.67375</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.1162499999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.395000000000001</v>
+        <v>-2.394999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.2224999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5750000000000008</v>
+        <v>-0.5749999999999995</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3887</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3685</v>
+      </c>
+      <c r="E75" t="n">
+        <v>202</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-111</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.87%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1611</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-1722</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-1723</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-7.008749999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="X75" t="n">
+        <v>5.571428571428571</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-1.728932584269663</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.06976744186046524</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.482790697674419</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
